--- a/src/test/resources/network/brightspots/rcv/test_data/continue_until_two_threshold_freeze/continue_until_two_threshold_freeze_cvr.xlsx
+++ b/src/test/resources/network/brightspots/rcv/test_data/continue_until_two_threshold_freeze/continue_until_two_threshold_freeze_cvr.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
   <si>
     <t>Ballot #</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>undervote</t>
   </si>
   <si>
     <t>B</t>
@@ -1233,8 +1236,12 @@
       <c r="B2" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" ht="13.55" customHeight="1">
@@ -1244,8 +1251,12 @@
       <c r="B3" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" ht="13.55" customHeight="1">
@@ -1255,8 +1266,12 @@
       <c r="B4" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" ht="13.55" customHeight="1">
@@ -1266,8 +1281,12 @@
       <c r="B5" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" ht="13.55" customHeight="1">
@@ -1277,8 +1296,12 @@
       <c r="B6" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" ht="13.55" customHeight="1">
@@ -1288,8 +1311,12 @@
       <c r="B7" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" ht="13.55" customHeight="1">
@@ -1299,8 +1326,12 @@
       <c r="B8" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" ht="13.55" customHeight="1">
@@ -1310,8 +1341,12 @@
       <c r="B9" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" ht="13.55" customHeight="1">
@@ -1319,10 +1354,14 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" ht="13.55" customHeight="1">
@@ -1330,10 +1369,14 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E11" s="3"/>
     </row>
     <row r="12" ht="13.55" customHeight="1">
@@ -1341,10 +1384,14 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" ht="13.55" customHeight="1">
@@ -1352,10 +1399,14 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" ht="13.55" customHeight="1">
@@ -1363,10 +1414,14 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" ht="13.55" customHeight="1">
@@ -1374,10 +1429,14 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" ht="13.55" customHeight="1">
@@ -1385,10 +1444,14 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" ht="13.55" customHeight="1">
@@ -1396,10 +1459,14 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E17" s="3"/>
     </row>
     <row r="18" ht="13.55" customHeight="1">
@@ -1407,10 +1474,14 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E18" s="3"/>
     </row>
   </sheetData>
